--- a/fabrinet/dist/20261025_Fabrinet模型_v0.1.1.xlsx
+++ b/fabrinet/dist/20261025_Fabrinet模型_v0.1.1.xlsx
@@ -6474,7 +6474,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6692,7 +6692,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6813,7 +6813,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6934,7 +6934,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7055,7 +7055,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7176,7 +7176,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.3.xlsx</t>
+      <t xml:space="preserve">_v0.3.1.xlsx</t>
     </r>
     <r>
       <rPr>
